--- a/review/etnografiya/may-december/accepted/march/march.xlsx
+++ b/review/etnografiya/may-december/accepted/march/march.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли из обрезков сшить вещь, которую будут беречь десятилетиями?</t>
+          <t xml:space="preserve">Лоскуты, оставшиеся от разных тканей, собираются в одеяло. Маленькие обрезки получают вторую жизнь — узор держится на терпении и точности шва.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -135,7 +135,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем бить стебли деревянной лопаткой, если из них хотят получить мягкую ткань?</t>
+          <t xml:space="preserve">Льняные стебли бьют деревянной трепалкой, чтобы отделить лишнее. Мягкость будущего полотна начинается с тяжёлой и совсем не мягкой работы.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -162,7 +162,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как из одного пучка получались и грубая верёвка, и тонкое полотно?</t>
+          <t xml:space="preserve">Из пучка льна выделяют волокно разного качества. Чесание разделяет будущие нити: материал для грубой работы и тонкого полотна готовят по-разному.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как хозяйка понимала, хватит ли пряжи на целый холст?</t>
+          <t xml:space="preserve">Пряжу считают и сматывают до начала ткачества. Будущий холст ещё не виден, но его размер уже требует точного домашнего расчёта.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нога нажала — между сотнями нитей появилась дорога. Как?</t>
+          <t xml:space="preserve">Нога нажимает подножку — между нитями открывается проход. Ткацкий стан переводит движение тела в порядок переплетения будущего холста.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -243,7 +243,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему ткацкий инструмент похож на маленькую лодку?</t>
+          <t xml:space="preserve">Челнок похож на лодку и несёт нить сквозь основу. Каждый проход оставляет новый ряд ткани — маленький инструмент работает на ширину полотна.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -270,7 +270,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Увидел фабричную машину — и вырезал свою. Разве так можно?</t>
+          <t xml:space="preserve">Увиденную машину мастер воспроизводит в дереве. Самодельное устройство хранит попытку понять чужой механизм и заставить его работать своими руками.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что превращает массовую открытку в обращение к одному человеку?</t>
+          <t xml:space="preserve">Открытку печатают для тысяч людей, а подпись адресуют одному. Несколько рукописных строк превращают массовую картинку в личное обращение.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем утюгу отверстия, если гладить должна его подошва?</t>
+          <t xml:space="preserve">Угольному утюгу нужен воздух: отверстия поддерживают жар внутри. Гладкая подошва скрывает маленькую топку, которую приходилось обслуживать.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -351,7 +351,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему нарядное полотенце берегли для событий, а не только для умывания?</t>
+          <t xml:space="preserve">Нарядное полотенце берегут для важных встреч и обрядов. Вышитая ткань участвует в событии, сохраняя больше смысла, чем обычная вещь для умывания.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Где у деревянной утки спряталась крышка?</t>
+          <t xml:space="preserve">Деревянная утка скрывает вместилище под крышкой. Скульптурная форма соединяет узнаваемую птицу с практической домашней вещью.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -405,7 +405,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как берёзовая кора превращается в посуду для питья?</t>
+          <t xml:space="preserve">Берёзовая кора становится сосудом для питья. В туесе природный материал получает форму посуды — соединения важны не меньше рисунка поверхности.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -432,7 +432,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у этого молочного сосуда нет ручки?</t>
+          <t xml:space="preserve">Молочный сосуд без ручки приходится брать за корпус. Форма привычной посуды направляет движение рук и хранит опыт ежедневного обращения.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -459,7 +459,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему один день зовут и Свистуньей, и Весновкой, и Плющихой?</t>
+          <t xml:space="preserve">Один день зовут Свистуньей, Весновкой и Плющихой. Народные названия сохраняют разные наблюдения за весной, а не единый прогноз погоды.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что делали со ступой в настоящем доме, пока Баба-яга летала в сказке?</t>
+          <t xml:space="preserve">В сказке ступа летает, в доме помогает обрабатывать зерно. Тяжёлый пест возвращает знакомому образу его настоящее рабочее назначение.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Куда исчезает зерно, которое насыпали в середину?</t>
+          <t xml:space="preserve">Зерно уходит между жерновами и выходит размолотым. Движение двух камней превращает запас урожая в основу будущей еды.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как прилёт грачей превращался в событие всей деревни?</t>
+          <t xml:space="preserve">Прилёт грачей становился заметным событием весны. Народный календарь сохраняет внимание к живой природе, от которой зависел годовой труд.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему одной сеткой нельзя одинаково просеять всё?</t>
+          <t xml:space="preserve">Мука и крупа требуют разного сита. Размер отверстий решает, что останется сверху, а что пройдёт сквозь сетку в другую посуду.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как учиться письму, если новая страница не нужна?</t>
+          <t xml:space="preserve">На грифельной доске пишут, стирают и пишут снова. Один предмет даёт ученику множество новых попыток без новой бумажной страницы.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем держать один нож сразу двумя руками?</t>
+          <t xml:space="preserve">Скобель держат двумя руками и тянут на себя. Лезвие снимает древесину контролируемым движением — форма будущей вещи появляется под усилием мастера.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как внутри нарядной глиняной фигуры помещается музыкальный инструмент?</t>
+          <t xml:space="preserve">Внутри глиняной фигурки скрыта полость свистульки. Нарядная игрушка становится инструментом: её голос зависит от устройства, а не только от росписи.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему весну встречали с птицей из теста в руках?</t>
+          <t xml:space="preserve">Весну встречают с птицей из теста в руках. Печёный жаворонок соединяет домашнюю работу с образом возвращения птиц и ожиданием тепла.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как плоские полоски лыка огибают человеческую стопу?</t>
+          <t xml:space="preserve">Плоские полоски лыка огибают стопу и образуют обувь. Лапоть держится на порядке переплетения — материал становится объёмом без тканого полотна.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как кусок кожи превращается в обувь?</t>
+          <t xml:space="preserve">Кусок кожи получает крой, сгибы и соединения. Обувь возникает из точной работы с плоской заготовкой, которой предстоит принять форму ноги.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему от старого орудия в музее могла остаться только железная часть?</t>
+          <t xml:space="preserve">От деревянного орудия может сохраниться только железная часть. Музейный остаток требует увидеть утраченную рукоять и работу целого предмета.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем ребёнку уменьшенная копия сельского орудия?</t>
+          <t xml:space="preserve">Ребёнку делают уменьшенное сельское орудие. Маленькая вещь показывает, как знакомство с трудом входило в повседневную жизнь семьи.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как пройти поле и не оставить пустую полосу?</t>
+          <t xml:space="preserve">Сеятель проходит поле и распределяет зерно рукой. Ровность будущего посева зависит от шага и размаха — точность рождается из освоенного движения.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что удерживает вместе десятки отдельных деревянных частей?</t>
+          <t xml:space="preserve">Десятки деревянных частей удерживаются соединениями. Колесо показывает, как отдельные заготовки становятся единой конструкцией под нагрузкой.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что заставляет часы идти, когда в них нет батарейки?</t>
+          <t xml:space="preserve">Часы идут без батарейки: механизм получает запас механической энергии. За циферблатом скрыта передача движения от детали к детали.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у одного дня столько водяных названий?</t>
+          <t xml:space="preserve">В народных именах весеннего дня слышится вода. Названия сохраняют сезонный опыт людей, внимательно следивших за таянием и течением.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как украсить бересту рисунком, не рисуя по ней кистью?</t>
+          <t xml:space="preserve">Бересту украшают без кисти — рисунок появляется от обработки поверхности. Узор рождается из свойств самой коры и точного движения инструмента.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
